--- a/NSO_01.07.2025.xlsx
+++ b/NSO_01.07.2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\InfPanel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{180E527A-D14E-4C16-AAAA-44371C6D9AE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88394578-18B9-4F54-80B0-3708DDD430C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2671" yWindow="2671" windowWidth="23631" windowHeight="12541" xr2:uid="{F8C46831-A766-4421-B6E6-28A897387E31}"/>
+    <workbookView xWindow="-111" yWindow="-111" windowWidth="31729" windowHeight="17342" xr2:uid="{F8C46831-A766-4421-B6E6-28A897387E31}"/>
   </bookViews>
   <sheets>
     <sheet name="page1" sheetId="1" r:id="rId1"/>
@@ -45,9 +45,6 @@
     <t>Уровень потребности в развитии дистанционного банковского обслуживания (Уровень потребности в ДБО)</t>
   </si>
   <si>
-    <t>Изменение уровня потребности в ДБО за счет создания альтернативной инфраструктуры, п.п.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Уровень потребности в ДБО с учетом созданной альтернативной инфраструктуры </t>
   </si>
   <si>
@@ -76,6 +73,9 @@
   </si>
   <si>
     <t>Новосибирская область</t>
+  </si>
+  <si>
+    <t>Изменение уровня потребности в ДБО за счет создания альтернативной инфраструктуры</t>
   </si>
 </sst>
 </file>
@@ -507,36 +507,36 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>10</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:12" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B2" s="1">
         <v>741396</v>
